--- a/artfynd/A 73981-2021 artfynd.xlsx
+++ b/artfynd/A 73981-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 73981-2021 artfynd.xlsx
+++ b/artfynd/A 73981-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>162491</v>
+        <v>81754369</v>
       </c>
       <c r="B2" t="n">
-        <v>104642</v>
+        <v>104643</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -708,34 +708,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skogsängen, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>683493.5662118184</v>
+        <v>683494.0382323122</v>
       </c>
       <c r="R2" t="n">
-        <v>6683006.675748603</v>
+        <v>6683007.196882401</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +745,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2009-07-20</t>
+          <t>2019-09-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -769,7 +755,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2009-07-20</t>
+          <t>2019-09-27</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -786,20 +772,16 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Åkerkant</t>
-        </is>
-      </c>
+      <c r="AR2" t="inlineStr"/>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jan-ola Helmersson</t>
+          <t>Daniel Tooke</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jan-ola Helmersson</t>
+          <t>Via Daniel Tooke</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -921,119 +903,6 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>81754369</v>
-      </c>
-      <c r="B4" t="n">
-        <v>104643</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>245</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Skogsklocka</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Campanula cervicaria</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Skogsängen, Upl</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>683494.0382323122</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6683007.196882401</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Östhammar</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Börstil</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2019-09-27</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2019-09-27</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Daniel Tooke</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Via Daniel Tooke</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 73981-2021 artfynd.xlsx
+++ b/artfynd/A 73981-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>81754369</v>
       </c>
       <c r="B2" t="n">
-        <v>104643</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>683494.0382323122</v>
+        <v>683494</v>
       </c>
       <c r="R2" t="n">
-        <v>6683007.196882401</v>
+        <v>6683007</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2019-09-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-09-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,54 +773,59 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>81754068</v>
+        <v>73862218</v>
       </c>
       <c r="B3" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5787</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221235</v>
+        <v>100555</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Krisslesköldbagge</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Cassida ferruginea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Goeze, 1777</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>slag-/vattenhåvning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skogsängen, Upl</t>
+          <t>Skogsängen, 300 m OSO, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>683520.2028871765</v>
+        <v>683482</v>
       </c>
       <c r="R3" t="n">
-        <v>6683011.994417506</v>
+        <v>6683005</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,22 +852,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-10-23</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-10-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-07-04</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>på krissla</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,20 +873,278 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>högörtäng i skogsbryn, med lövsly, tistlar, rödklint, krissla mm</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Inula salicina</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Inula salicina</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>Håkan Ljungberg</t>
+        </is>
       </c>
       <c r="AR3" t="inlineStr"/>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Håkan Ljungberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Håkan Ljungberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>104872265</v>
+      </c>
+      <c r="B4" t="n">
+        <v>5787</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100555</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Krisslesköldbagge</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cassida ferruginea</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Goeze, 1777</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>slaghåvning</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Skogsängen OSO, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>683471</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6683023</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>på krissla</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>slänt mellan skogsbryn och åker. Örtvegetation av krissla, rödklint mm, lövsly</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>krissla</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pentanema salicinum</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Pentanema salicinum</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Håkan Ljungberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Håkan Ljungberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>81754068</v>
+      </c>
+      <c r="B5" t="n">
+        <v>102241</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skogsängen, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>683520</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6683012</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2019-10-23</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2019-10-23</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Daniel Tooke</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Daniel Tooke</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 73981-2021 artfynd.xlsx
+++ b/artfynd/A 73981-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81754369</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -907,6 +917,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73862218</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1043,6 +1058,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104872265</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1145,8 +1165,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81754068</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>